--- a/sheets/top_ratings.xlsx
+++ b/sheets/top_ratings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Weiminh\Desktop\test\sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Weiminh\Documents\My Documents\ratings\sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D860845B-AB83-4557-ACE5-AFC6F3B3A01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B8E7FA-C66E-48AF-ADA2-A7F218E3D081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="-110" windowWidth="18290" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,12 +91,6 @@
     <t>Spider-Man</t>
   </si>
   <si>
-    <t>X-Men: First Class</t>
-  </si>
-  <si>
-    <t>This Is the End</t>
-  </si>
-  <si>
     <t>Pokémon: The First Movie</t>
   </si>
   <si>
@@ -109,9 +103,6 @@
     <t>Lloyd in Space</t>
   </si>
   <si>
-    <t>The Walking Dead</t>
-  </si>
-  <si>
     <t>The Weekenders</t>
   </si>
   <si>
@@ -128,6 +119,15 @@
   </si>
   <si>
     <t>The Adventures of Jimmy Neutron: Boy Genius</t>
+  </si>
+  <si>
+    <t>Futurama</t>
+  </si>
+  <si>
+    <t>A Goofy Movie</t>
+  </si>
+  <si>
+    <t>Digimon: The Movie</t>
   </si>
 </sst>
 </file>
@@ -717,51 +717,49 @@
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1"/>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -781,7 +779,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.6328125" customWidth="1"/>
@@ -794,62 +792,65 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>26</v>
+      <c r="A4" t="s">
+        <v>28</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
+      <c r="A11" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B11" s="1"/>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
